--- a/base_creditas.xlsx
+++ b/base_creditas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC8EE55-2AC5-4444-A6F1-8E8818503240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA0AC05-A0C1-4AA1-A928-C8A1CDAA1F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -487,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W110"/>
+  <dimension ref="A1:W128"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -1914,10 +1914,10 @@
         <v>270</v>
       </c>
       <c r="K21">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L21">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="M21">
         <v>37</v>
@@ -1935,16 +1935,16 @@
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="R21" s="5">
-        <v>0.26669999999999999</v>
-      </c>
-      <c r="S21" s="5">
-        <v>0.25</v>
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="S21" s="3">
+        <v>1</v>
       </c>
       <c r="T21">
-        <v>17</v>
-      </c>
-      <c r="U21" s="3">
-        <v>0.31480000000000002</v>
+        <v>-37</v>
+      </c>
+      <c r="U21" t="s">
+        <v>25</v>
       </c>
       <c r="V21" s="5">
         <v>0.8679</v>
@@ -1985,10 +1985,10 @@
         <v>147</v>
       </c>
       <c r="K22">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L22">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="M22">
         <v>21</v>
@@ -2006,16 +2006,16 @@
         <v>8.6999999999999994E-3</v>
       </c>
       <c r="R22" s="5">
-        <v>0.2041</v>
-      </c>
-      <c r="S22" s="5">
-        <v>0.26669999999999999</v>
+        <v>0.1905</v>
+      </c>
+      <c r="S22" s="3">
+        <v>1</v>
       </c>
       <c r="T22">
-        <v>1</v>
-      </c>
-      <c r="U22" s="3">
-        <v>4.5499999999999999E-2</v>
+        <v>-21</v>
+      </c>
+      <c r="U22" t="s">
+        <v>25</v>
       </c>
       <c r="V22" s="5">
         <v>1</v>
@@ -2056,10 +2056,10 @@
         <v>135</v>
       </c>
       <c r="K23">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L23">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="M23">
         <v>19</v>
@@ -2076,17 +2076,17 @@
       <c r="Q23" s="5">
         <v>6.6E-3</v>
       </c>
-      <c r="R23" s="3">
-        <v>0.2074</v>
-      </c>
-      <c r="S23" s="5">
-        <v>0.32140000000000002</v>
+      <c r="R23" s="5">
+        <v>0.1852</v>
+      </c>
+      <c r="S23" s="3">
+        <v>1</v>
       </c>
       <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3">
-        <v>0</v>
+        <v>-19</v>
+      </c>
+      <c r="U23" t="s">
+        <v>25</v>
       </c>
       <c r="V23" s="5">
         <v>0.88239999999999996</v>
@@ -2201,7 +2201,7 @@
         <v>2</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25">
         <v>2</v>
@@ -2222,13 +2222,13 @@
         <v>0.22220000000000001</v>
       </c>
       <c r="S25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25" s="3">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="U25" t="s">
+        <v>25</v>
       </c>
       <c r="V25" s="5">
         <v>1</v>
@@ -2269,10 +2269,10 @@
         <v>241</v>
       </c>
       <c r="K26">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L26">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="M26">
         <v>25</v>
@@ -2290,16 +2290,16 @@
         <v>1.1900000000000001E-2</v>
       </c>
       <c r="R26" s="5">
-        <v>0.19500000000000001</v>
-      </c>
-      <c r="S26" s="5">
-        <v>0.31909999999999999</v>
+        <v>0.18260000000000001</v>
+      </c>
+      <c r="S26" s="3">
+        <v>1</v>
       </c>
       <c r="T26">
-        <v>7</v>
-      </c>
-      <c r="U26" s="5">
-        <v>0.21879999999999999</v>
+        <v>-25</v>
+      </c>
+      <c r="U26" t="s">
+        <v>25</v>
       </c>
       <c r="V26" s="5">
         <v>0.87880000000000003</v>
@@ -2343,7 +2343,7 @@
         <v>59</v>
       </c>
       <c r="L27">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="M27">
         <v>33</v>
@@ -2363,14 +2363,14 @@
       <c r="R27" s="5">
         <v>0.36199999999999999</v>
       </c>
-      <c r="S27" s="5">
-        <v>0.38979999999999998</v>
+      <c r="S27" s="3">
+        <v>1</v>
       </c>
       <c r="T27">
-        <v>3</v>
-      </c>
-      <c r="U27" s="5">
-        <v>8.3299999999999999E-2</v>
+        <v>-33</v>
+      </c>
+      <c r="U27" t="s">
+        <v>25</v>
       </c>
       <c r="W27">
         <v>16.956</v>
@@ -2408,10 +2408,10 @@
         <v>186</v>
       </c>
       <c r="K28">
-        <v>237</v>
+        <v>43</v>
       </c>
       <c r="L28">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="M28">
         <v>21</v>
@@ -2429,16 +2429,16 @@
         <v>1.3299999999999999E-2</v>
       </c>
       <c r="R28" s="5">
-        <v>1.274</v>
-      </c>
-      <c r="S28" s="5">
-        <v>7.17E-2</v>
+        <v>0.23119999999999999</v>
+      </c>
+      <c r="S28" s="3">
+        <v>1</v>
       </c>
       <c r="T28">
-        <v>199</v>
-      </c>
-      <c r="U28" s="5">
-        <v>0.90449999999999997</v>
+        <v>-21</v>
+      </c>
+      <c r="U28" t="s">
+        <v>25</v>
       </c>
       <c r="V28" s="5">
         <v>0.6774</v>
@@ -2479,10 +2479,10 @@
         <v>285</v>
       </c>
       <c r="K29">
-        <v>150</v>
+        <v>83</v>
       </c>
       <c r="L29">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="M29">
         <v>33</v>
@@ -2500,16 +2500,16 @@
         <v>3.1300000000000001E-2</v>
       </c>
       <c r="R29" s="5">
-        <v>0.52629999999999999</v>
-      </c>
-      <c r="S29" s="5">
-        <v>0.33329999999999999</v>
+        <v>0.29120000000000001</v>
+      </c>
+      <c r="S29" s="3">
+        <v>1</v>
       </c>
       <c r="T29">
-        <v>67</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0.67</v>
+        <v>-33</v>
+      </c>
+      <c r="U29" t="s">
+        <v>25</v>
       </c>
       <c r="W29">
         <v>7.8479999999999999</v>
@@ -2550,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30">
         <v>1</v>
@@ -2571,13 +2571,13 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="S30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30" s="3">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="U30" t="s">
+        <v>25</v>
       </c>
       <c r="V30" s="5">
         <v>0</v>
@@ -2618,7 +2618,7 @@
         <v>32</v>
       </c>
       <c r="L31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M31">
         <v>4</v>
@@ -2638,14 +2638,14 @@
       <c r="R31" s="5">
         <v>0.34039999999999998</v>
       </c>
-      <c r="S31" s="5">
-        <v>0.875</v>
+      <c r="S31" s="3">
+        <v>1</v>
       </c>
       <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31" s="3">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="U31" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
@@ -2680,10 +2680,10 @@
         <v>232</v>
       </c>
       <c r="K32">
-        <v>3482</v>
+        <v>35</v>
       </c>
       <c r="L32">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="M32">
         <v>18</v>
@@ -2701,16 +2701,16 @@
         <v>1.24E-2</v>
       </c>
       <c r="R32" s="5">
-        <v>15</v>
-      </c>
-      <c r="S32" s="5">
-        <v>4.5999999999999999E-3</v>
+        <v>0.15090000000000001</v>
+      </c>
+      <c r="S32" s="3">
+        <v>1</v>
       </c>
       <c r="T32">
-        <v>3448</v>
-      </c>
-      <c r="U32" s="5">
-        <v>0.99480000000000002</v>
+        <v>-18</v>
+      </c>
+      <c r="U32" t="s">
+        <v>25</v>
       </c>
       <c r="V32" s="5">
         <v>0.95240000000000002</v>
@@ -2748,10 +2748,10 @@
         <v>250</v>
       </c>
       <c r="K33">
-        <v>2839</v>
+        <v>53</v>
       </c>
       <c r="L33">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="M33">
         <v>26</v>
@@ -2769,16 +2769,16 @@
         <v>1.24E-2</v>
       </c>
       <c r="R33" s="5">
-        <v>11.35</v>
-      </c>
-      <c r="S33" s="5">
-        <v>7.0000000000000001E-3</v>
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="S33" s="3">
+        <v>1</v>
       </c>
       <c r="T33">
-        <v>2793</v>
-      </c>
-      <c r="U33" s="5">
-        <v>0.99080000000000001</v>
+        <v>-26</v>
+      </c>
+      <c r="U33" t="s">
+        <v>25</v>
       </c>
       <c r="V33" s="5">
         <v>0.85289999999999999</v>
@@ -2816,10 +2816,10 @@
         <v>121</v>
       </c>
       <c r="K34">
-        <v>3038</v>
+        <v>17</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="M34">
         <v>13</v>
@@ -2837,16 +2837,16 @@
         <v>0.01</v>
       </c>
       <c r="R34" s="5">
-        <v>25.1</v>
-      </c>
-      <c r="S34" s="5">
-        <v>1.6000000000000001E-3</v>
+        <v>0.14050000000000001</v>
+      </c>
+      <c r="S34" s="3">
+        <v>1</v>
       </c>
       <c r="T34">
-        <v>3020</v>
-      </c>
-      <c r="U34" s="5">
-        <v>0.99570000000000003</v>
+        <v>-13</v>
+      </c>
+      <c r="U34" t="s">
+        <v>25</v>
       </c>
       <c r="V34" s="5">
         <v>1</v>
@@ -2884,10 +2884,10 @@
         <v>315</v>
       </c>
       <c r="K35">
-        <v>949</v>
+        <v>80</v>
       </c>
       <c r="L35">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="M35">
         <v>58</v>
@@ -2905,16 +2905,16 @@
         <v>3.7199999999999997E-2</v>
       </c>
       <c r="R35" s="5">
-        <v>3.012</v>
-      </c>
-      <c r="S35" s="5">
-        <v>1.0500000000000001E-2</v>
+        <v>0.254</v>
+      </c>
+      <c r="S35" s="3">
+        <v>1</v>
       </c>
       <c r="T35">
-        <v>881</v>
-      </c>
-      <c r="U35" s="5">
-        <v>0.93820000000000003</v>
+        <v>-58</v>
+      </c>
+      <c r="U35" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
@@ -2949,10 +2949,10 @@
         <v>85</v>
       </c>
       <c r="K36">
-        <v>2828</v>
+        <v>17</v>
       </c>
       <c r="L36">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="M36">
         <v>10</v>
@@ -2969,17 +2969,17 @@
       <c r="Q36" s="5">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="R36" s="5">
-        <v>33.270000000000003</v>
-      </c>
-      <c r="S36" s="5">
-        <v>2.5000000000000001E-3</v>
+      <c r="R36" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="S36" s="3">
+        <v>1</v>
       </c>
       <c r="T36">
-        <v>2811</v>
-      </c>
-      <c r="U36" s="5">
-        <v>0.99650000000000005</v>
+        <v>-10</v>
+      </c>
+      <c r="U36" t="s">
+        <v>25</v>
       </c>
       <c r="V36" s="5">
         <v>1</v>
@@ -3017,10 +3017,10 @@
         <v>232</v>
       </c>
       <c r="K37">
-        <v>511</v>
+        <v>50</v>
       </c>
       <c r="L37">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="M37">
         <v>4</v>
@@ -3038,16 +3038,16 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="R37" s="5">
-        <v>2.202</v>
-      </c>
-      <c r="S37" s="5">
-        <v>7.2400000000000006E-2</v>
+        <v>0.2155</v>
+      </c>
+      <c r="S37" s="3">
+        <v>1</v>
       </c>
       <c r="T37">
-        <v>470</v>
-      </c>
-      <c r="U37" s="5">
-        <v>0.99160000000000004</v>
+        <v>-4</v>
+      </c>
+      <c r="U37" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.3">
@@ -3082,10 +3082,10 @@
         <v>182</v>
       </c>
       <c r="K38">
-        <v>3255</v>
+        <v>26</v>
       </c>
       <c r="L38">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="M38">
         <v>14</v>
@@ -3103,16 +3103,16 @@
         <v>1.2800000000000001E-2</v>
       </c>
       <c r="R38" s="5">
-        <v>17.88</v>
-      </c>
-      <c r="S38" s="5">
-        <v>3.3999999999999998E-3</v>
+        <v>0.1429</v>
+      </c>
+      <c r="S38" s="3">
+        <v>1</v>
       </c>
       <c r="T38">
-        <v>3230</v>
-      </c>
-      <c r="U38" s="5">
-        <v>0.99570000000000003</v>
+        <v>-14</v>
+      </c>
+      <c r="U38" t="s">
+        <v>25</v>
       </c>
       <c r="V38" s="5">
         <v>1</v>
@@ -3150,10 +3150,10 @@
         <v>123</v>
       </c>
       <c r="K39">
-        <v>524</v>
+        <v>30</v>
       </c>
       <c r="L39">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="M39">
         <v>11</v>
@@ -3171,16 +3171,16 @@
         <v>2.8500000000000001E-2</v>
       </c>
       <c r="R39" s="5">
-        <v>4.26</v>
-      </c>
-      <c r="S39" s="5">
-        <v>1.15E-2</v>
+        <v>0.24390000000000001</v>
+      </c>
+      <c r="S39" s="3">
+        <v>1</v>
       </c>
       <c r="T39">
-        <v>507</v>
-      </c>
-      <c r="U39" s="5">
-        <v>0.9788</v>
+        <v>-11</v>
+      </c>
+      <c r="U39" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
@@ -3215,10 +3215,10 @@
         <v>72</v>
       </c>
       <c r="K40">
-        <v>1917</v>
+        <v>12</v>
       </c>
       <c r="L40">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M40">
         <v>7</v>
@@ -3236,16 +3236,16 @@
         <v>1.1599999999999999E-2</v>
       </c>
       <c r="R40" s="5">
-        <v>26.62</v>
-      </c>
-      <c r="S40" s="5">
-        <v>3.0999999999999999E-3</v>
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="S40" s="3">
+        <v>1</v>
       </c>
       <c r="T40">
-        <v>1904</v>
-      </c>
-      <c r="U40" s="5">
-        <v>0.99629999999999996</v>
+        <v>-7</v>
+      </c>
+      <c r="U40" t="s">
+        <v>25</v>
       </c>
       <c r="V40" s="5">
         <v>1</v>
@@ -3283,10 +3283,10 @@
         <v>87</v>
       </c>
       <c r="K41">
-        <v>244</v>
+        <v>17</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M41">
         <v>11</v>
@@ -3304,16 +3304,16 @@
         <v>2.3400000000000001E-2</v>
       </c>
       <c r="R41" s="5">
-        <v>2.8039999999999998</v>
-      </c>
-      <c r="S41" s="5">
-        <v>2.46E-2</v>
+        <v>0.19539999999999999</v>
+      </c>
+      <c r="S41" s="3">
+        <v>1</v>
       </c>
       <c r="T41">
-        <v>227</v>
-      </c>
-      <c r="U41" s="5">
-        <v>0.95379999999999998</v>
+        <v>-11</v>
+      </c>
+      <c r="U41" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
@@ -3348,10 +3348,10 @@
         <v>153</v>
       </c>
       <c r="K42">
-        <v>3147</v>
+        <v>29</v>
       </c>
       <c r="L42">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="M42">
         <v>16</v>
@@ -3369,16 +3369,16 @@
         <v>1.29E-2</v>
       </c>
       <c r="R42" s="5">
-        <v>20.56</v>
-      </c>
-      <c r="S42" s="5">
-        <v>4.4000000000000003E-3</v>
+        <v>0.1895</v>
+      </c>
+      <c r="S42" s="3">
+        <v>1</v>
       </c>
       <c r="T42">
-        <v>3117</v>
-      </c>
-      <c r="U42" s="5">
-        <v>0.99490000000000001</v>
+        <v>-16</v>
+      </c>
+      <c r="U42" t="s">
+        <v>25</v>
       </c>
       <c r="V42" s="5">
         <v>1</v>
@@ -3416,10 +3416,10 @@
         <v>130</v>
       </c>
       <c r="K43">
-        <v>723</v>
+        <v>38</v>
       </c>
       <c r="L43">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="M43">
         <v>17</v>
@@ -3437,16 +3437,16 @@
         <v>3.7900000000000003E-2</v>
       </c>
       <c r="R43" s="5">
-        <v>5.5609999999999999</v>
-      </c>
-      <c r="S43" s="5">
-        <v>2.9000000000000001E-2</v>
+        <v>0.2923</v>
+      </c>
+      <c r="S43" s="3">
+        <v>1</v>
       </c>
       <c r="T43">
-        <v>685</v>
-      </c>
-      <c r="U43" s="5">
-        <v>0.9758</v>
+        <v>-17</v>
+      </c>
+      <c r="U43" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
@@ -3481,10 +3481,10 @@
         <v>262</v>
       </c>
       <c r="K44">
-        <v>3217</v>
+        <v>41</v>
       </c>
       <c r="L44">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="M44">
         <v>29</v>
@@ -3502,16 +3502,16 @@
         <v>1.55E-2</v>
       </c>
       <c r="R44" s="5">
-        <v>12.27</v>
-      </c>
-      <c r="S44" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.1565</v>
+      </c>
+      <c r="S44" s="3">
+        <v>1</v>
       </c>
       <c r="T44">
-        <v>3175</v>
-      </c>
-      <c r="U44" s="5">
-        <v>0.9909</v>
+        <v>-29</v>
+      </c>
+      <c r="U44" t="s">
+        <v>25</v>
       </c>
       <c r="V44" s="5">
         <v>1</v>
@@ -3549,10 +3549,10 @@
         <v>121</v>
       </c>
       <c r="K45">
-        <v>1057</v>
+        <v>25</v>
       </c>
       <c r="L45">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M45">
         <v>15</v>
@@ -3570,16 +3570,16 @@
         <v>3.09E-2</v>
       </c>
       <c r="R45" s="5">
-        <v>8.7349999999999994</v>
-      </c>
-      <c r="S45" s="5">
-        <v>9.4999999999999998E-3</v>
+        <v>0.20660000000000001</v>
+      </c>
+      <c r="S45" s="3">
+        <v>1</v>
       </c>
       <c r="T45">
-        <v>1032</v>
-      </c>
-      <c r="U45" s="5">
-        <v>0.98570000000000002</v>
+        <v>-15</v>
+      </c>
+      <c r="U45" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.3">
@@ -3614,10 +3614,10 @@
         <v>282</v>
       </c>
       <c r="K46">
-        <v>3228</v>
+        <v>45</v>
       </c>
       <c r="L46">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="M46">
         <v>27</v>
@@ -3635,16 +3635,16 @@
         <v>1.6299999999999999E-2</v>
       </c>
       <c r="R46" s="5">
-        <v>11.44</v>
-      </c>
-      <c r="S46" s="5">
-        <v>5.5999999999999999E-3</v>
+        <v>0.15959999999999999</v>
+      </c>
+      <c r="S46" s="3">
+        <v>1</v>
       </c>
       <c r="T46">
-        <v>3183</v>
-      </c>
-      <c r="U46" s="5">
-        <v>0.99160000000000004</v>
+        <v>-27</v>
+      </c>
+      <c r="U46" t="s">
+        <v>25</v>
       </c>
       <c r="V46" s="5">
         <v>1</v>
@@ -3682,10 +3682,10 @@
         <v>192</v>
       </c>
       <c r="K47">
-        <v>1073</v>
+        <v>40</v>
       </c>
       <c r="L47">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="M47">
         <v>28</v>
@@ -3703,16 +3703,16 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="R47" s="5">
-        <v>5.5880000000000001</v>
-      </c>
-      <c r="S47" s="5">
-        <v>1.21E-2</v>
+        <v>0.20830000000000001</v>
+      </c>
+      <c r="S47" s="3">
+        <v>1</v>
       </c>
       <c r="T47">
-        <v>1032</v>
-      </c>
-      <c r="U47" s="5">
-        <v>0.97360000000000002</v>
+        <v>-28</v>
+      </c>
+      <c r="U47" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
@@ -3747,10 +3747,10 @@
         <v>261</v>
       </c>
       <c r="K48">
-        <v>1314</v>
+        <v>59</v>
       </c>
       <c r="L48">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -3768,16 +3768,16 @@
         <v>1.0800000000000001E-2</v>
       </c>
       <c r="R48" s="5">
-        <v>5.0339999999999998</v>
-      </c>
-      <c r="S48" s="5">
-        <v>2.4400000000000002E-2</v>
+        <v>0.2261</v>
+      </c>
+      <c r="S48" s="3">
+        <v>1</v>
       </c>
       <c r="T48">
-        <v>1282</v>
-      </c>
-      <c r="U48" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U48" t="s">
+        <v>25</v>
       </c>
       <c r="V48" s="5">
         <v>1</v>
@@ -3815,10 +3815,10 @@
         <v>240</v>
       </c>
       <c r="K49">
-        <v>552</v>
+        <v>53</v>
       </c>
       <c r="L49">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -3835,17 +3835,17 @@
       <c r="Q49" s="5">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="R49" s="3">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="S49" s="5">
-        <v>3.2599999999999997E-2</v>
+      <c r="R49" s="5">
+        <v>0.2208</v>
+      </c>
+      <c r="S49" s="3">
+        <v>1</v>
       </c>
       <c r="T49">
-        <v>534</v>
-      </c>
-      <c r="U49" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U49" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.3">
@@ -3880,10 +3880,10 @@
         <v>277</v>
       </c>
       <c r="K50">
-        <v>2341</v>
+        <v>38</v>
       </c>
       <c r="L50">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="M50">
         <v>0</v>
@@ -3901,16 +3901,16 @@
         <v>9.7999999999999997E-3</v>
       </c>
       <c r="R50" s="5">
-        <v>8.4510000000000005</v>
-      </c>
-      <c r="S50" s="5">
-        <v>6.4000000000000003E-3</v>
+        <v>0.13719999999999999</v>
+      </c>
+      <c r="S50" s="3">
+        <v>1</v>
       </c>
       <c r="T50">
-        <v>2326</v>
-      </c>
-      <c r="U50" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U50" t="s">
+        <v>25</v>
       </c>
       <c r="V50" t="s">
         <v>25</v>
@@ -3948,10 +3948,10 @@
         <v>298</v>
       </c>
       <c r="K51">
-        <v>1075</v>
+        <v>65</v>
       </c>
       <c r="L51">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -3969,16 +3969,16 @@
         <v>2.8899999999999999E-2</v>
       </c>
       <c r="R51" s="5">
-        <v>3.6070000000000002</v>
-      </c>
-      <c r="S51" s="5">
-        <v>1.49E-2</v>
+        <v>0.21809999999999999</v>
+      </c>
+      <c r="S51" s="3">
+        <v>1</v>
       </c>
       <c r="T51">
-        <v>1059</v>
-      </c>
-      <c r="U51" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U51" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
@@ -4013,7 +4013,7 @@
         <v>1</v>
       </c>
       <c r="K52">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -4034,16 +4034,16 @@
         <v>4.1000000000000003E-3</v>
       </c>
       <c r="R52" s="3">
-        <v>39</v>
-      </c>
-      <c r="S52" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="S52" t="s">
+        <v>25</v>
       </c>
       <c r="T52">
-        <v>39</v>
-      </c>
-      <c r="U52" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U52" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.3">
@@ -4078,7 +4078,7 @@
         <v>3</v>
       </c>
       <c r="K53">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -4098,17 +4098,17 @@
       <c r="Q53" s="5">
         <v>1.8200000000000001E-2</v>
       </c>
-      <c r="R53" s="5">
-        <v>7.3330000000000002</v>
-      </c>
-      <c r="S53" s="3">
-        <v>0</v>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" t="s">
+        <v>25</v>
       </c>
       <c r="T53">
-        <v>22</v>
-      </c>
-      <c r="U53" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U53" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.3">
@@ -4143,10 +4143,10 @@
         <v>189</v>
       </c>
       <c r="K54">
-        <v>212</v>
+        <v>35</v>
       </c>
       <c r="L54">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -4164,16 +4164,16 @@
         <v>1.67E-2</v>
       </c>
       <c r="R54" s="5">
-        <v>1.121</v>
-      </c>
-      <c r="S54" s="5">
-        <v>5.6599999999999998E-2</v>
+        <v>0.1852</v>
+      </c>
+      <c r="S54" s="3">
+        <v>1</v>
       </c>
       <c r="T54">
-        <v>200</v>
-      </c>
-      <c r="U54" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U54" t="s">
+        <v>25</v>
       </c>
       <c r="V54" t="s">
         <v>25</v>
@@ -4211,10 +4211,10 @@
         <v>139</v>
       </c>
       <c r="K55">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="L55">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="M55">
         <v>0</v>
@@ -4232,16 +4232,16 @@
         <v>3.0200000000000001E-2</v>
       </c>
       <c r="R55" s="5">
-        <v>0.74819999999999998</v>
-      </c>
-      <c r="S55" s="5">
-        <v>6.7299999999999999E-2</v>
+        <v>0.2374</v>
+      </c>
+      <c r="S55" s="3">
+        <v>1</v>
       </c>
       <c r="T55">
-        <v>97</v>
-      </c>
-      <c r="U55" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U55" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.3">
@@ -4276,10 +4276,10 @@
         <v>91</v>
       </c>
       <c r="K56">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L56">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="M56">
         <v>18</v>
@@ -4297,16 +4297,16 @@
         <v>1.2699999999999999E-2</v>
       </c>
       <c r="R56" s="5">
-        <v>0.32969999999999999</v>
-      </c>
-      <c r="S56" s="5">
-        <v>0.36670000000000003</v>
+        <v>0.28570000000000001</v>
+      </c>
+      <c r="S56" s="3">
+        <v>1</v>
       </c>
       <c r="T56">
-        <v>1</v>
-      </c>
-      <c r="U56" s="5">
-        <v>5.2600000000000001E-2</v>
+        <v>-18</v>
+      </c>
+      <c r="U56" t="s">
+        <v>25</v>
       </c>
       <c r="V56" s="5">
         <v>1</v>
@@ -4344,10 +4344,10 @@
         <v>183</v>
       </c>
       <c r="K57">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L57">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="M57">
         <v>41</v>
@@ -4365,16 +4365,16 @@
         <v>2.6100000000000002E-2</v>
       </c>
       <c r="R57" s="5">
-        <v>0.25679999999999997</v>
-      </c>
-      <c r="S57" s="5">
-        <v>0.10639999999999999</v>
+        <v>0.2404</v>
+      </c>
+      <c r="S57" s="3">
+        <v>1</v>
       </c>
       <c r="T57">
-        <v>1</v>
-      </c>
-      <c r="U57" s="5">
-        <v>2.3800000000000002E-2</v>
+        <v>-41</v>
+      </c>
+      <c r="U57" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.3">
@@ -4409,10 +4409,10 @@
         <v>161</v>
       </c>
       <c r="K58">
-        <v>3436</v>
+        <v>33</v>
       </c>
       <c r="L58">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="M58">
         <v>19</v>
@@ -4430,16 +4430,16 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="R58" s="5">
-        <v>21.34</v>
-      </c>
-      <c r="S58" s="5">
-        <v>4.8999999999999998E-3</v>
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="S58" s="3">
+        <v>1</v>
       </c>
       <c r="T58">
-        <v>3400</v>
-      </c>
-      <c r="U58" s="5">
-        <v>0.99439999999999995</v>
+        <v>-19</v>
+      </c>
+      <c r="U58" t="s">
+        <v>25</v>
       </c>
       <c r="V58" s="5">
         <v>1</v>
@@ -4477,10 +4477,10 @@
         <v>127</v>
       </c>
       <c r="K59">
-        <v>1262</v>
+        <v>34</v>
       </c>
       <c r="L59">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="M59">
         <v>25</v>
@@ -4498,16 +4498,16 @@
         <v>2.3800000000000002E-2</v>
       </c>
       <c r="R59" s="5">
-        <v>9.9369999999999994</v>
-      </c>
-      <c r="S59" s="5">
-        <v>7.1000000000000004E-3</v>
+        <v>0.26769999999999999</v>
+      </c>
+      <c r="S59" s="3">
+        <v>1</v>
       </c>
       <c r="T59">
-        <v>1228</v>
-      </c>
-      <c r="U59" s="3">
-        <v>0.98</v>
+        <v>-25</v>
+      </c>
+      <c r="U59" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.3">
@@ -4542,10 +4542,10 @@
         <v>181</v>
       </c>
       <c r="K60">
-        <v>3683</v>
+        <v>40</v>
       </c>
       <c r="L60">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="M60">
         <v>24</v>
@@ -4563,16 +4563,16 @@
         <v>1.11E-2</v>
       </c>
       <c r="R60" s="5">
-        <v>20.34</v>
-      </c>
-      <c r="S60" s="5">
-        <v>4.8999999999999998E-3</v>
+        <v>0.221</v>
+      </c>
+      <c r="S60" s="3">
+        <v>1</v>
       </c>
       <c r="T60">
-        <v>3641</v>
-      </c>
-      <c r="U60" s="5">
-        <v>0.99350000000000005</v>
+        <v>-24</v>
+      </c>
+      <c r="U60" t="s">
+        <v>25</v>
       </c>
       <c r="V60" s="5">
         <v>1</v>
@@ -4610,10 +4610,10 @@
         <v>52</v>
       </c>
       <c r="K61">
-        <v>521</v>
+        <v>8</v>
       </c>
       <c r="L61">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M61">
         <v>3</v>
@@ -4631,16 +4631,16 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="R61" s="5">
-        <v>10.01</v>
-      </c>
-      <c r="S61" s="5">
-        <v>3.8E-3</v>
+        <v>0.15379999999999999</v>
+      </c>
+      <c r="S61" s="3">
+        <v>1</v>
       </c>
       <c r="T61">
-        <v>516</v>
-      </c>
-      <c r="U61" s="5">
-        <v>0.99419999999999997</v>
+        <v>-3</v>
+      </c>
+      <c r="U61" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.3">
@@ -4675,10 +4675,10 @@
         <v>157</v>
       </c>
       <c r="K62">
-        <v>3426</v>
+        <v>38</v>
       </c>
       <c r="L62">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="M62">
         <v>17</v>
@@ -4696,16 +4696,16 @@
         <v>9.1999999999999998E-3</v>
       </c>
       <c r="R62" s="5">
-        <v>21.82</v>
-      </c>
-      <c r="S62" s="5">
-        <v>6.4000000000000003E-3</v>
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="S62" s="3">
+        <v>1</v>
       </c>
       <c r="T62">
-        <v>3387</v>
-      </c>
-      <c r="U62" s="5">
-        <v>0.995</v>
+        <v>-17</v>
+      </c>
+      <c r="U62" t="s">
+        <v>25</v>
       </c>
       <c r="V62" s="5">
         <v>1</v>
@@ -4743,10 +4743,10 @@
         <v>49</v>
       </c>
       <c r="K63">
-        <v>441</v>
+        <v>13</v>
       </c>
       <c r="L63">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -4763,17 +4763,17 @@
       <c r="Q63" s="5">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="R63" s="3">
-        <v>9</v>
-      </c>
-      <c r="S63" s="5">
-        <v>1.1299999999999999E-2</v>
+      <c r="R63" s="5">
+        <v>0.26529999999999998</v>
+      </c>
+      <c r="S63" s="3">
+        <v>1</v>
       </c>
       <c r="T63">
-        <v>436</v>
-      </c>
-      <c r="U63" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U63" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.3">
@@ -4808,10 +4808,10 @@
         <v>157</v>
       </c>
       <c r="K64">
-        <v>2905</v>
+        <v>35</v>
       </c>
       <c r="L64">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="M64">
         <v>19</v>
@@ -4829,16 +4829,16 @@
         <v>8.3999999999999995E-3</v>
       </c>
       <c r="R64" s="5">
-        <v>18.5</v>
-      </c>
-      <c r="S64" s="5">
-        <v>7.1999999999999998E-3</v>
+        <v>0.22289999999999999</v>
+      </c>
+      <c r="S64" s="3">
+        <v>1</v>
       </c>
       <c r="T64">
-        <v>2865</v>
-      </c>
-      <c r="U64" s="5">
-        <v>0.99339999999999995</v>
+        <v>-19</v>
+      </c>
+      <c r="U64" t="s">
+        <v>25</v>
       </c>
       <c r="V64" s="5">
         <v>1</v>
@@ -4876,10 +4876,10 @@
         <v>16</v>
       </c>
       <c r="K65">
-        <v>137</v>
+        <v>4</v>
       </c>
       <c r="L65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M65">
         <v>0</v>
@@ -4896,17 +4896,17 @@
       <c r="Q65" s="5">
         <v>1.7399999999999999E-2</v>
       </c>
-      <c r="R65" s="5">
-        <v>8.5619999999999994</v>
-      </c>
-      <c r="S65" s="5">
-        <v>7.3000000000000001E-3</v>
+      <c r="R65" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="S65" s="3">
+        <v>1</v>
       </c>
       <c r="T65">
-        <v>136</v>
-      </c>
-      <c r="U65" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U65" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.3">
@@ -4941,10 +4941,10 @@
         <v>182</v>
       </c>
       <c r="K66">
-        <v>1112</v>
+        <v>29</v>
       </c>
       <c r="L66">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="M66">
         <v>15</v>
@@ -4962,16 +4962,16 @@
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="R66" s="5">
-        <v>6.109</v>
-      </c>
-      <c r="S66" s="5">
-        <v>9.9000000000000008E-3</v>
+        <v>0.1593</v>
+      </c>
+      <c r="S66" s="3">
+        <v>1</v>
       </c>
       <c r="T66">
-        <v>1086</v>
-      </c>
-      <c r="U66" s="5">
-        <v>0.98640000000000005</v>
+        <v>-15</v>
+      </c>
+      <c r="U66" t="s">
+        <v>25</v>
       </c>
       <c r="V66" s="5">
         <v>0.9</v>
@@ -5009,10 +5009,10 @@
         <v>94</v>
       </c>
       <c r="K67">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="L67">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="M67">
         <v>15</v>
@@ -5030,16 +5030,16 @@
         <v>4.0800000000000003E-2</v>
       </c>
       <c r="R67" s="5">
-        <v>1.595</v>
-      </c>
-      <c r="S67" s="5">
-        <v>2.6700000000000002E-2</v>
+        <v>0.21279999999999999</v>
+      </c>
+      <c r="S67" s="3">
+        <v>1</v>
       </c>
       <c r="T67">
-        <v>131</v>
-      </c>
-      <c r="U67" s="5">
-        <v>0.89729999999999999</v>
+        <v>-15</v>
+      </c>
+      <c r="U67" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.3">
@@ -5074,10 +5074,10 @@
         <v>171</v>
       </c>
       <c r="K68">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L68">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="M68">
         <v>18</v>
@@ -5095,16 +5095,16 @@
         <v>1.1599999999999999E-2</v>
       </c>
       <c r="R68" s="5">
-        <v>0.18709999999999999</v>
-      </c>
-      <c r="S68" s="5">
-        <v>0.40629999999999999</v>
+        <v>0.1696</v>
+      </c>
+      <c r="S68" s="3">
+        <v>1</v>
       </c>
       <c r="T68">
-        <v>1</v>
-      </c>
-      <c r="U68" s="5">
-        <v>5.2600000000000001E-2</v>
+        <v>-18</v>
+      </c>
+      <c r="U68" t="s">
+        <v>25</v>
       </c>
       <c r="V68" s="5">
         <v>1</v>
@@ -5145,7 +5145,7 @@
         <v>37</v>
       </c>
       <c r="L69">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="M69">
         <v>30</v>
@@ -5165,14 +5165,14 @@
       <c r="R69" s="5">
         <v>0.22700000000000001</v>
       </c>
-      <c r="S69" s="5">
-        <v>0.18920000000000001</v>
+      <c r="S69" s="3">
+        <v>1</v>
       </c>
       <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69" s="3">
-        <v>0</v>
+        <v>-30</v>
+      </c>
+      <c r="U69" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.3">
@@ -5207,10 +5207,10 @@
         <v>157</v>
       </c>
       <c r="K70">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="L70">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="M70">
         <v>11</v>
@@ -5228,16 +5228,16 @@
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="R70" s="5">
-        <v>0.36309999999999998</v>
-      </c>
-      <c r="S70" s="5">
-        <v>0.52629999999999999</v>
+        <v>0.2611</v>
+      </c>
+      <c r="S70" s="3">
+        <v>1</v>
       </c>
       <c r="T70">
-        <v>16</v>
-      </c>
-      <c r="U70" s="5">
-        <v>0.59260000000000002</v>
+        <v>-11</v>
+      </c>
+      <c r="U70" t="s">
+        <v>25</v>
       </c>
       <c r="V70" s="5">
         <v>1</v>
@@ -5275,10 +5275,10 @@
         <v>253</v>
       </c>
       <c r="K71">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="L71">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="M71">
         <v>40</v>
@@ -5296,16 +5296,16 @@
         <v>2.8299999999999999E-2</v>
       </c>
       <c r="R71" s="5">
-        <v>0.2964</v>
-      </c>
-      <c r="S71" s="5">
-        <v>0.33329999999999999</v>
+        <v>0.25690000000000002</v>
+      </c>
+      <c r="S71" s="3">
+        <v>1</v>
       </c>
       <c r="T71">
-        <v>10</v>
-      </c>
-      <c r="U71" s="3">
-        <v>0.2</v>
+        <v>-40</v>
+      </c>
+      <c r="U71" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.3">
@@ -5340,10 +5340,10 @@
         <v>117</v>
       </c>
       <c r="K72">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="L72">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M72">
         <v>11</v>
@@ -5361,16 +5361,16 @@
         <v>6.7999999999999996E-3</v>
       </c>
       <c r="R72" s="5">
-        <v>0.30769999999999997</v>
-      </c>
-      <c r="S72" s="5">
-        <v>0.52780000000000005</v>
+        <v>0.23930000000000001</v>
+      </c>
+      <c r="S72" s="3">
+        <v>1</v>
       </c>
       <c r="T72">
-        <v>6</v>
-      </c>
-      <c r="U72" s="5">
-        <v>0.35289999999999999</v>
+        <v>-11</v>
+      </c>
+      <c r="U72" t="s">
+        <v>25</v>
       </c>
       <c r="V72" s="5">
         <v>1</v>
@@ -5411,7 +5411,7 @@
         <v>39</v>
       </c>
       <c r="L73">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="M73">
         <v>13</v>
@@ -5431,14 +5431,14 @@
       <c r="R73" s="5">
         <v>0.24529999999999999</v>
       </c>
-      <c r="S73" s="5">
-        <v>0.28210000000000002</v>
+      <c r="S73" s="3">
+        <v>1</v>
       </c>
       <c r="T73">
-        <v>15</v>
-      </c>
-      <c r="U73" s="5">
-        <v>0.53569999999999995</v>
+        <v>-13</v>
+      </c>
+      <c r="U73" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.3">
@@ -5606,10 +5606,10 @@
         <v>138</v>
       </c>
       <c r="K76">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="L76">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="M76">
         <v>0</v>
@@ -5627,16 +5627,16 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="R76" s="5">
-        <v>0.28989999999999999</v>
+        <v>0.21010000000000001</v>
       </c>
       <c r="S76" s="3">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="T76">
-        <v>22</v>
-      </c>
-      <c r="U76" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U76" t="s">
+        <v>25</v>
       </c>
       <c r="V76" t="s">
         <v>25</v>
@@ -5674,10 +5674,10 @@
         <v>143</v>
       </c>
       <c r="K77">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L77">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="M77">
         <v>0</v>
@@ -5695,16 +5695,16 @@
         <v>1.8200000000000001E-2</v>
       </c>
       <c r="R77" s="5">
-        <v>0.2238</v>
-      </c>
-      <c r="S77" s="5">
-        <v>0.28129999999999999</v>
+        <v>0.20280000000000001</v>
+      </c>
+      <c r="S77" s="3">
+        <v>1</v>
       </c>
       <c r="T77">
-        <v>23</v>
-      </c>
-      <c r="U77" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U77" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.3">
@@ -5739,10 +5739,10 @@
         <v>163</v>
       </c>
       <c r="K78">
-        <v>1068</v>
+        <v>48</v>
       </c>
       <c r="L78">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="M78">
         <v>20</v>
@@ -5760,16 +5760,16 @@
         <v>9.1999999999999998E-3</v>
       </c>
       <c r="R78" s="5">
-        <v>6.5519999999999996</v>
-      </c>
-      <c r="S78" s="5">
-        <v>2.9000000000000001E-2</v>
+        <v>0.29449999999999998</v>
+      </c>
+      <c r="S78" s="3">
+        <v>1</v>
       </c>
       <c r="T78">
-        <v>1017</v>
-      </c>
-      <c r="U78" s="5">
-        <v>0.98070000000000002</v>
+        <v>-20</v>
+      </c>
+      <c r="U78" t="s">
+        <v>25</v>
       </c>
       <c r="V78" s="5">
         <v>1</v>
@@ -5807,10 +5807,10 @@
         <v>93</v>
       </c>
       <c r="K79">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="L79">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="M79">
         <v>14</v>
@@ -5828,16 +5828,16 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="R79" s="5">
-        <v>3.01</v>
-      </c>
-      <c r="S79" s="5">
-        <v>3.2099999999999997E-2</v>
+        <v>0.3226</v>
+      </c>
+      <c r="S79" s="3">
+        <v>1</v>
       </c>
       <c r="T79">
-        <v>257</v>
-      </c>
-      <c r="U79" s="5">
-        <v>0.94830000000000003</v>
+        <v>-14</v>
+      </c>
+      <c r="U79" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.3">
@@ -5872,10 +5872,10 @@
         <v>165</v>
       </c>
       <c r="K80">
-        <v>1685</v>
+        <v>48</v>
       </c>
       <c r="L80">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="M80">
         <v>25</v>
@@ -5893,16 +5893,16 @@
         <v>7.6E-3</v>
       </c>
       <c r="R80" s="5">
-        <v>10.210000000000001</v>
-      </c>
-      <c r="S80" s="5">
-        <v>1.3599999999999999E-2</v>
+        <v>0.29089999999999999</v>
+      </c>
+      <c r="S80" s="3">
+        <v>1</v>
       </c>
       <c r="T80">
-        <v>1637</v>
-      </c>
-      <c r="U80" s="5">
-        <v>0.98499999999999999</v>
+        <v>-25</v>
+      </c>
+      <c r="U80" t="s">
+        <v>25</v>
       </c>
       <c r="V80" s="5">
         <v>1</v>
@@ -5940,10 +5940,10 @@
         <v>75</v>
       </c>
       <c r="K81">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="L81">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M81">
         <v>8</v>
@@ -5960,17 +5960,17 @@
       <c r="Q81" s="5">
         <v>2.9600000000000001E-2</v>
       </c>
-      <c r="R81" s="5">
-        <v>1.0129999999999999</v>
-      </c>
-      <c r="S81" s="5">
-        <v>5.2600000000000001E-2</v>
+      <c r="R81" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="S81" s="3">
+        <v>1</v>
       </c>
       <c r="T81">
-        <v>64</v>
-      </c>
-      <c r="U81" s="5">
-        <v>0.88890000000000002</v>
+        <v>-8</v>
+      </c>
+      <c r="U81" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.3">
@@ -6005,10 +6005,10 @@
         <v>141</v>
       </c>
       <c r="K82">
-        <v>2061</v>
+        <v>40</v>
       </c>
       <c r="L82">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="M82">
         <v>15</v>
@@ -6026,16 +6026,16 @@
         <v>7.9000000000000008E-3</v>
       </c>
       <c r="R82" s="5">
-        <v>14.61</v>
-      </c>
-      <c r="S82" s="5">
-        <v>1.3599999999999999E-2</v>
+        <v>0.28370000000000001</v>
+      </c>
+      <c r="S82" s="3">
+        <v>1</v>
       </c>
       <c r="T82">
-        <v>2018</v>
-      </c>
-      <c r="U82" s="5">
-        <v>0.99260000000000004</v>
+        <v>-15</v>
+      </c>
+      <c r="U82" t="s">
+        <v>25</v>
       </c>
       <c r="V82" s="5">
         <v>1</v>
@@ -6073,10 +6073,10 @@
         <v>119</v>
       </c>
       <c r="K83">
-        <v>231</v>
+        <v>25</v>
       </c>
       <c r="L83">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="M83">
         <v>17</v>
@@ -6094,16 +6094,16 @@
         <v>4.2200000000000001E-2</v>
       </c>
       <c r="R83" s="5">
-        <v>1.9410000000000001</v>
-      </c>
-      <c r="S83" s="5">
-        <v>1.7299999999999999E-2</v>
+        <v>0.21010000000000001</v>
+      </c>
+      <c r="S83" s="3">
+        <v>1</v>
       </c>
       <c r="T83">
-        <v>210</v>
-      </c>
-      <c r="U83" s="5">
-        <v>0.92510000000000003</v>
+        <v>-17</v>
+      </c>
+      <c r="U83" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.3">
@@ -6138,10 +6138,10 @@
         <v>209</v>
       </c>
       <c r="K84">
-        <v>4079</v>
+        <v>39</v>
       </c>
       <c r="L84">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="M84">
         <v>16</v>
@@ -6159,16 +6159,16 @@
         <v>6.7000000000000002E-3</v>
       </c>
       <c r="R84" s="5">
-        <v>19.510000000000002</v>
-      </c>
-      <c r="S84" s="5">
-        <v>6.4000000000000003E-3</v>
+        <v>0.18659999999999999</v>
+      </c>
+      <c r="S84" s="3">
+        <v>1</v>
       </c>
       <c r="T84">
-        <v>4037</v>
-      </c>
-      <c r="U84" s="5">
-        <v>0.99609999999999999</v>
+        <v>-16</v>
+      </c>
+      <c r="U84" t="s">
+        <v>25</v>
       </c>
       <c r="V84" s="5">
         <v>1</v>
@@ -6206,10 +6206,10 @@
         <v>51</v>
       </c>
       <c r="K85">
-        <v>208</v>
+        <v>20</v>
       </c>
       <c r="L85">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M85">
         <v>12</v>
@@ -6227,16 +6227,16 @@
         <v>3.9399999999999998E-2</v>
       </c>
       <c r="R85" s="5">
-        <v>4.0780000000000003</v>
-      </c>
-      <c r="S85" s="5">
-        <v>1.44E-2</v>
+        <v>0.39219999999999999</v>
+      </c>
+      <c r="S85" s="3">
+        <v>1</v>
       </c>
       <c r="T85">
-        <v>193</v>
-      </c>
-      <c r="U85" s="5">
-        <v>0.9415</v>
+        <v>-12</v>
+      </c>
+      <c r="U85" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.3">
@@ -6271,10 +6271,10 @@
         <v>227</v>
       </c>
       <c r="K86">
-        <v>4284</v>
+        <v>44</v>
       </c>
       <c r="L86">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="M86">
         <v>21</v>
@@ -6292,16 +6292,16 @@
         <v>7.1000000000000004E-3</v>
       </c>
       <c r="R86" s="5">
-        <v>18.87</v>
-      </c>
-      <c r="S86" s="5">
-        <v>6.1000000000000004E-3</v>
+        <v>0.1938</v>
+      </c>
+      <c r="S86" s="3">
+        <v>1</v>
       </c>
       <c r="T86">
-        <v>4237</v>
-      </c>
-      <c r="U86" s="5">
-        <v>0.99509999999999998</v>
+        <v>-21</v>
+      </c>
+      <c r="U86" t="s">
+        <v>25</v>
       </c>
       <c r="V86" s="5">
         <v>1</v>
@@ -6339,10 +6339,10 @@
         <v>72</v>
       </c>
       <c r="K87">
-        <v>1575</v>
+        <v>18</v>
       </c>
       <c r="L87">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M87">
         <v>7</v>
@@ -6359,17 +6359,17 @@
       <c r="Q87" s="5">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="R87" s="5">
-        <v>21.87</v>
-      </c>
-      <c r="S87" s="5">
-        <v>8.3000000000000001E-3</v>
+      <c r="R87" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="S87" s="3">
+        <v>1</v>
       </c>
       <c r="T87">
-        <v>1555</v>
-      </c>
-      <c r="U87" s="5">
-        <v>0.99550000000000005</v>
+        <v>-7</v>
+      </c>
+      <c r="U87" t="s">
+        <v>25</v>
       </c>
       <c r="V87" s="5">
         <v>1</v>
@@ -6407,10 +6407,10 @@
         <v>140</v>
       </c>
       <c r="K88">
-        <v>1634</v>
+        <v>25</v>
       </c>
       <c r="L88">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="M88">
         <v>10</v>
@@ -6428,16 +6428,16 @@
         <v>7.1000000000000004E-3</v>
       </c>
       <c r="R88" s="5">
-        <v>11.67</v>
-      </c>
-      <c r="S88" s="5">
-        <v>9.7999999999999997E-3</v>
+        <v>0.17860000000000001</v>
+      </c>
+      <c r="S88" s="3">
+        <v>1</v>
       </c>
       <c r="T88">
-        <v>1608</v>
-      </c>
-      <c r="U88" s="5">
-        <v>0.99380000000000002</v>
+        <v>-10</v>
+      </c>
+      <c r="U88" t="s">
+        <v>25</v>
       </c>
       <c r="V88" s="5">
         <v>1</v>
@@ -6475,10 +6475,10 @@
         <v>240</v>
       </c>
       <c r="K89">
-        <v>1300</v>
+        <v>72</v>
       </c>
       <c r="L89">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="M89">
         <v>16</v>
@@ -6495,17 +6495,17 @@
       <c r="Q89" s="5">
         <v>7.6E-3</v>
       </c>
-      <c r="R89" s="5">
-        <v>5.4160000000000004</v>
-      </c>
-      <c r="S89" s="5">
-        <v>4.3799999999999999E-2</v>
+      <c r="R89" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="S89" s="3">
+        <v>1</v>
       </c>
       <c r="T89">
-        <v>1227</v>
-      </c>
-      <c r="U89" s="5">
-        <v>0.98709999999999998</v>
+        <v>-16</v>
+      </c>
+      <c r="U89" t="s">
+        <v>25</v>
       </c>
       <c r="V89" s="5">
         <v>1</v>
@@ -6543,10 +6543,10 @@
         <v>140</v>
       </c>
       <c r="K90">
-        <v>1897</v>
+        <v>41</v>
       </c>
       <c r="L90">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="M90">
         <v>10</v>
@@ -6563,17 +6563,17 @@
       <c r="Q90" s="5">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="R90" s="3">
-        <v>13.55</v>
-      </c>
-      <c r="S90" s="5">
-        <v>1.6299999999999999E-2</v>
+      <c r="R90" s="5">
+        <v>0.29289999999999999</v>
+      </c>
+      <c r="S90" s="3">
+        <v>1</v>
       </c>
       <c r="T90">
-        <v>1856</v>
-      </c>
-      <c r="U90" s="5">
-        <v>0.99460000000000004</v>
+        <v>-10</v>
+      </c>
+      <c r="U90" t="s">
+        <v>25</v>
       </c>
       <c r="V90" s="5">
         <v>0.92310000000000003</v>
@@ -6611,7 +6611,7 @@
         <v>2</v>
       </c>
       <c r="K91">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -6632,16 +6632,16 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R91" s="3">
-        <v>36.5</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="S91" t="s">
+        <v>25</v>
       </c>
       <c r="T91">
-        <v>73</v>
-      </c>
-      <c r="U91" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U91" t="s">
+        <v>25</v>
       </c>
       <c r="V91" t="s">
         <v>25</v>
@@ -6679,10 +6679,10 @@
         <v>112</v>
       </c>
       <c r="K92">
-        <v>2143</v>
+        <v>28</v>
       </c>
       <c r="L92">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="M92">
         <v>7</v>
@@ -6699,17 +6699,17 @@
       <c r="Q92" s="5">
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="R92" s="5">
-        <v>19.13</v>
-      </c>
-      <c r="S92" s="5">
-        <v>9.2999999999999992E-3</v>
+      <c r="R92" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="S92" s="3">
+        <v>1</v>
       </c>
       <c r="T92">
-        <v>2116</v>
-      </c>
-      <c r="U92" s="5">
-        <v>0.99670000000000003</v>
+        <v>-7</v>
+      </c>
+      <c r="U92" t="s">
+        <v>25</v>
       </c>
       <c r="V92" s="5">
         <v>1</v>
@@ -6747,10 +6747,10 @@
         <v>234</v>
       </c>
       <c r="K93">
-        <v>3917</v>
+        <v>70</v>
       </c>
       <c r="L93">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="M93">
         <v>14</v>
@@ -6768,16 +6768,16 @@
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="R93" s="5">
-        <v>16.73</v>
-      </c>
-      <c r="S93" s="5">
-        <v>1.5100000000000001E-2</v>
+        <v>0.29909999999999998</v>
+      </c>
+      <c r="S93" s="3">
+        <v>1</v>
       </c>
       <c r="T93">
-        <v>3844</v>
-      </c>
-      <c r="U93" s="5">
-        <v>0.99639999999999995</v>
+        <v>-14</v>
+      </c>
+      <c r="U93" t="s">
+        <v>25</v>
       </c>
       <c r="V93" s="5">
         <v>1</v>
@@ -6815,10 +6815,10 @@
         <v>138</v>
       </c>
       <c r="K94">
-        <v>3319</v>
+        <v>40</v>
       </c>
       <c r="L94">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M94">
         <v>12</v>
@@ -6836,16 +6836,16 @@
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="R94" s="5">
-        <v>24.05</v>
-      </c>
-      <c r="S94" s="5">
-        <v>8.6999999999999994E-3</v>
+        <v>0.28989999999999999</v>
+      </c>
+      <c r="S94" s="3">
+        <v>1</v>
       </c>
       <c r="T94">
-        <v>3278</v>
-      </c>
-      <c r="U94" s="5">
-        <v>0.99639999999999995</v>
+        <v>-12</v>
+      </c>
+      <c r="U94" t="s">
+        <v>25</v>
       </c>
       <c r="V94" s="5">
         <v>1</v>
@@ -6883,10 +6883,10 @@
         <v>107</v>
       </c>
       <c r="K95">
-        <v>1495</v>
+        <v>30</v>
       </c>
       <c r="L95">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M95">
         <v>16</v>
@@ -6904,16 +6904,16 @@
         <v>4.8999999999999998E-3</v>
       </c>
       <c r="R95" s="5">
-        <v>13.97</v>
+        <v>0.28039999999999998</v>
       </c>
       <c r="S95" s="3">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="T95">
-        <v>1464</v>
-      </c>
-      <c r="U95" s="5">
-        <v>0.98919999999999997</v>
+        <v>-16</v>
+      </c>
+      <c r="U95" t="s">
+        <v>25</v>
       </c>
       <c r="V95" s="5">
         <v>1</v>
@@ -6951,10 +6951,10 @@
         <v>85</v>
       </c>
       <c r="K96">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L96">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M96">
         <v>7</v>
@@ -6972,16 +6972,16 @@
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="R96" s="5">
-        <v>0.32940000000000003</v>
-      </c>
-      <c r="S96" s="5">
-        <v>0.57140000000000002</v>
+        <v>0.25879999999999997</v>
+      </c>
+      <c r="S96" s="3">
+        <v>1</v>
       </c>
       <c r="T96">
-        <v>5</v>
-      </c>
-      <c r="U96" s="5">
-        <v>0.41670000000000001</v>
+        <v>-7</v>
+      </c>
+      <c r="U96" t="s">
+        <v>25</v>
       </c>
       <c r="V96" s="5">
         <v>1</v>
@@ -7019,10 +7019,10 @@
         <v>126</v>
       </c>
       <c r="K97">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="L97">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M97">
         <v>5</v>
@@ -7040,16 +7040,16 @@
         <v>7.7000000000000002E-3</v>
       </c>
       <c r="R97" s="5">
-        <v>0.23019999999999999</v>
-      </c>
-      <c r="S97" s="5">
-        <v>0.48280000000000001</v>
+        <v>0.1429</v>
+      </c>
+      <c r="S97" s="3">
+        <v>1</v>
       </c>
       <c r="T97">
-        <v>10</v>
-      </c>
-      <c r="U97" s="5">
-        <v>0.66669999999999996</v>
+        <v>-5</v>
+      </c>
+      <c r="U97" t="s">
+        <v>25</v>
       </c>
       <c r="V97" s="5">
         <v>1</v>
@@ -7087,10 +7087,10 @@
         <v>115</v>
       </c>
       <c r="K98">
-        <v>1105</v>
+        <v>18</v>
       </c>
       <c r="L98">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M98">
         <v>8</v>
@@ -7108,16 +7108,16 @@
         <v>6.8999999999999999E-3</v>
       </c>
       <c r="R98" s="5">
-        <v>9.6080000000000005</v>
+        <v>0.1565</v>
       </c>
       <c r="S98" s="3">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="T98">
-        <v>1086</v>
-      </c>
-      <c r="U98" s="5">
-        <v>0.99270000000000003</v>
+        <v>-8</v>
+      </c>
+      <c r="U98" t="s">
+        <v>25</v>
       </c>
       <c r="V98" s="5">
         <v>1</v>
@@ -7155,10 +7155,10 @@
         <v>121</v>
       </c>
       <c r="K99">
-        <v>821</v>
+        <v>17</v>
       </c>
       <c r="L99">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M99">
         <v>6</v>
@@ -7176,16 +7176,16 @@
         <v>7.6E-3</v>
       </c>
       <c r="R99" s="5">
-        <v>6.7850000000000001</v>
-      </c>
-      <c r="S99" s="5">
-        <v>1.34E-2</v>
+        <v>0.14050000000000001</v>
+      </c>
+      <c r="S99" s="3">
+        <v>1</v>
       </c>
       <c r="T99">
-        <v>804</v>
-      </c>
-      <c r="U99" s="5">
-        <v>0.99260000000000004</v>
+        <v>-6</v>
+      </c>
+      <c r="U99" t="s">
+        <v>25</v>
       </c>
       <c r="V99" s="5">
         <v>1</v>
@@ -7223,10 +7223,10 @@
         <v>200</v>
       </c>
       <c r="K100">
-        <v>656</v>
+        <v>59</v>
       </c>
       <c r="L100">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="M100">
         <v>10</v>
@@ -7243,17 +7243,17 @@
       <c r="Q100" s="5">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="R100" s="3">
-        <v>3.28</v>
-      </c>
-      <c r="S100" s="5">
-        <v>7.4700000000000003E-2</v>
+      <c r="R100" s="5">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="S100" s="3">
+        <v>1</v>
       </c>
       <c r="T100">
-        <v>597</v>
-      </c>
-      <c r="U100" s="5">
-        <v>0.98350000000000004</v>
+        <v>-10</v>
+      </c>
+      <c r="U100" t="s">
+        <v>25</v>
       </c>
       <c r="V100" s="5">
         <v>1</v>
@@ -7359,10 +7359,10 @@
         <v>132</v>
       </c>
       <c r="K102">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L102">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="M102">
         <v>13</v>
@@ -7380,16 +7380,16 @@
         <v>1.15E-2</v>
       </c>
       <c r="R102" s="5">
-        <v>0.39389999999999997</v>
-      </c>
-      <c r="S102" s="5">
-        <v>0.73080000000000001</v>
+        <v>0.37880000000000003</v>
+      </c>
+      <c r="S102" s="3">
+        <v>1</v>
       </c>
       <c r="T102">
-        <v>1</v>
-      </c>
-      <c r="U102" s="5">
-        <v>7.1400000000000005E-2</v>
+        <v>-13</v>
+      </c>
+      <c r="U102" t="s">
+        <v>25</v>
       </c>
       <c r="V102" s="5">
         <v>1</v>
@@ -7430,10 +7430,10 @@
         <v>259</v>
       </c>
       <c r="K103">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L103">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="M103">
         <v>30</v>
@@ -7451,16 +7451,16 @@
         <v>8.3999999999999995E-3</v>
       </c>
       <c r="R103" s="5">
-        <v>0.34360000000000002</v>
-      </c>
-      <c r="S103" s="5">
-        <v>0.57299999999999995</v>
+        <v>0.31659999999999999</v>
+      </c>
+      <c r="S103" s="3">
+        <v>1</v>
       </c>
       <c r="T103">
-        <v>8</v>
-      </c>
-      <c r="U103" s="5">
-        <v>0.21049999999999999</v>
+        <v>-30</v>
+      </c>
+      <c r="U103" t="s">
+        <v>25</v>
       </c>
       <c r="V103" s="5">
         <v>0.9677</v>
@@ -7501,10 +7501,10 @@
         <v>240</v>
       </c>
       <c r="K104">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L104">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M104">
         <v>1</v>
@@ -7521,17 +7521,17 @@
       <c r="Q104" s="5">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="R104" s="5">
-        <v>0.26669999999999999</v>
-      </c>
-      <c r="S104" s="5">
-        <v>0.92190000000000005</v>
+      <c r="R104" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="S104" s="3">
+        <v>1</v>
       </c>
       <c r="T104">
-        <v>4</v>
-      </c>
-      <c r="U104" s="3">
-        <v>0.8</v>
+        <v>-1</v>
+      </c>
+      <c r="U104" t="s">
+        <v>25</v>
       </c>
       <c r="V104" s="5">
         <v>1</v>
@@ -7572,7 +7572,7 @@
         <v>220</v>
       </c>
       <c r="K105">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L105">
         <v>35</v>
@@ -7593,16 +7593,16 @@
         <v>9.2999999999999992E-3</v>
       </c>
       <c r="R105" s="5">
-        <v>0.18179999999999999</v>
-      </c>
-      <c r="S105" s="5">
-        <v>0.875</v>
+        <v>0.15909999999999999</v>
+      </c>
+      <c r="S105" s="3">
+        <v>1</v>
       </c>
       <c r="T105">
-        <v>5</v>
-      </c>
-      <c r="U105" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U105" t="s">
+        <v>25</v>
       </c>
       <c r="V105" t="s">
         <v>25</v>
@@ -7643,7 +7643,7 @@
         <v>239</v>
       </c>
       <c r="K106">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L106">
         <v>28</v>
@@ -7664,16 +7664,16 @@
         <v>1.06E-2</v>
       </c>
       <c r="R106" s="5">
-        <v>0.13389999999999999</v>
-      </c>
-      <c r="S106" s="5">
-        <v>0.875</v>
+        <v>0.1172</v>
+      </c>
+      <c r="S106" s="3">
+        <v>1</v>
       </c>
       <c r="T106">
-        <v>4</v>
-      </c>
-      <c r="U106" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U106" t="s">
+        <v>25</v>
       </c>
       <c r="V106" t="s">
         <v>25</v>
@@ -7714,7 +7714,7 @@
         <v>216</v>
       </c>
       <c r="K107">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="L107">
         <v>51</v>
@@ -7735,16 +7735,16 @@
         <v>0.01</v>
       </c>
       <c r="R107" s="5">
-        <v>0.25459999999999999</v>
-      </c>
-      <c r="S107" s="5">
-        <v>0.92730000000000001</v>
+        <v>0.2361</v>
+      </c>
+      <c r="S107" s="3">
+        <v>1</v>
       </c>
       <c r="T107">
-        <v>4</v>
-      </c>
-      <c r="U107" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U107" t="s">
+        <v>25</v>
       </c>
       <c r="V107" t="s">
         <v>25</v>
@@ -7785,7 +7785,7 @@
         <v>487</v>
       </c>
       <c r="K108">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="L108">
         <v>145</v>
@@ -7806,16 +7806,16 @@
         <v>1.04E-2</v>
       </c>
       <c r="R108" s="5">
-        <v>0.31619999999999998</v>
-      </c>
-      <c r="S108" s="5">
-        <v>0.94159999999999999</v>
+        <v>0.29770000000000002</v>
+      </c>
+      <c r="S108" s="3">
+        <v>1</v>
       </c>
       <c r="T108">
-        <v>9</v>
-      </c>
-      <c r="U108" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U108" t="s">
+        <v>25</v>
       </c>
       <c r="V108" t="s">
         <v>25</v>
@@ -7856,10 +7856,10 @@
         <v>270</v>
       </c>
       <c r="K109">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L109">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="M109">
         <v>29</v>
@@ -7877,16 +7877,16 @@
         <v>8.6E-3</v>
       </c>
       <c r="R109" s="5">
-        <v>0.30370000000000003</v>
-      </c>
-      <c r="S109" s="5">
-        <v>0.46339999999999998</v>
+        <v>0.29260000000000003</v>
+      </c>
+      <c r="S109" s="3">
+        <v>1</v>
       </c>
       <c r="T109">
-        <v>15</v>
-      </c>
-      <c r="U109" s="5">
-        <v>0.34089999999999998</v>
+        <v>-29</v>
+      </c>
+      <c r="U109" t="s">
+        <v>25</v>
       </c>
       <c r="V109" s="5">
         <v>0.78569999999999995</v>
@@ -7957,6 +7957,1281 @@
         <v>0</v>
       </c>
       <c r="U110" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B111">
+        <v>9</v>
+      </c>
+      <c r="C111">
+        <v>81</v>
+      </c>
+      <c r="D111">
+        <v>85</v>
+      </c>
+      <c r="E111" t="s">
+        <v>27</v>
+      </c>
+      <c r="F111">
+        <v>9736</v>
+      </c>
+      <c r="G111">
+        <v>25</v>
+      </c>
+      <c r="H111">
+        <v>7</v>
+      </c>
+      <c r="I111">
+        <v>23715</v>
+      </c>
+      <c r="J111">
+        <v>271</v>
+      </c>
+      <c r="K111">
+        <v>85</v>
+      </c>
+      <c r="L111">
+        <v>43</v>
+      </c>
+      <c r="M111">
+        <v>42</v>
+      </c>
+      <c r="N111">
+        <v>5</v>
+      </c>
+      <c r="O111" s="4">
+        <v>1.0069444444444444E-3</v>
+      </c>
+      <c r="P111" s="4">
+        <v>1.3194444444444445E-3</v>
+      </c>
+      <c r="Q111" s="5">
+        <v>1.14E-2</v>
+      </c>
+      <c r="R111" s="5">
+        <v>0.31369999999999998</v>
+      </c>
+      <c r="S111" s="5">
+        <v>0.50590000000000002</v>
+      </c>
+      <c r="T111">
+        <v>0</v>
+      </c>
+      <c r="U111" s="3">
+        <v>0</v>
+      </c>
+      <c r="V111" s="5">
+        <v>0.97440000000000004</v>
+      </c>
+      <c r="W111">
+        <v>47.375999999999998</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B112">
+        <v>10</v>
+      </c>
+      <c r="C112">
+        <v>81</v>
+      </c>
+      <c r="D112">
+        <v>85</v>
+      </c>
+      <c r="E112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F112">
+        <v>9736</v>
+      </c>
+      <c r="G112">
+        <v>25</v>
+      </c>
+      <c r="H112">
+        <v>11</v>
+      </c>
+      <c r="I112">
+        <v>35588</v>
+      </c>
+      <c r="J112">
+        <v>304</v>
+      </c>
+      <c r="K112">
+        <v>89</v>
+      </c>
+      <c r="L112">
+        <v>42</v>
+      </c>
+      <c r="M112">
+        <v>47</v>
+      </c>
+      <c r="N112">
+        <v>3</v>
+      </c>
+      <c r="O112" s="4">
+        <v>1.3425925925925925E-3</v>
+      </c>
+      <c r="P112" s="4">
+        <v>1.8634259259259259E-3</v>
+      </c>
+      <c r="Q112" s="5">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="R112" s="5">
+        <v>0.2928</v>
+      </c>
+      <c r="S112" s="5">
+        <v>0.47189999999999999</v>
+      </c>
+      <c r="T112">
+        <v>0</v>
+      </c>
+      <c r="U112" s="3">
+        <v>0</v>
+      </c>
+      <c r="V112" s="5">
+        <v>0.95920000000000005</v>
+      </c>
+      <c r="W112">
+        <v>44.16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B113">
+        <v>11</v>
+      </c>
+      <c r="C113">
+        <v>81</v>
+      </c>
+      <c r="D113">
+        <v>85</v>
+      </c>
+      <c r="E113" t="s">
+        <v>27</v>
+      </c>
+      <c r="F113">
+        <v>9736</v>
+      </c>
+      <c r="G113">
+        <v>25</v>
+      </c>
+      <c r="H113">
+        <v>11</v>
+      </c>
+      <c r="I113">
+        <v>32331</v>
+      </c>
+      <c r="J113">
+        <v>224</v>
+      </c>
+      <c r="K113">
+        <v>66</v>
+      </c>
+      <c r="L113">
+        <v>31</v>
+      </c>
+      <c r="M113">
+        <v>35</v>
+      </c>
+      <c r="N113">
+        <v>1</v>
+      </c>
+      <c r="O113" s="4">
+        <v>1.6550925925925926E-3</v>
+      </c>
+      <c r="P113" s="4">
+        <v>1.0300925925925926E-3</v>
+      </c>
+      <c r="Q113" s="5">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="R113" s="5">
+        <v>0.29459999999999997</v>
+      </c>
+      <c r="S113" s="5">
+        <v>0.46970000000000001</v>
+      </c>
+      <c r="T113">
+        <v>0</v>
+      </c>
+      <c r="U113" s="3">
+        <v>0</v>
+      </c>
+      <c r="V113" s="5">
+        <v>1</v>
+      </c>
+      <c r="W113">
+        <v>33.851999999999997</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B114">
+        <v>11</v>
+      </c>
+      <c r="C114">
+        <v>84</v>
+      </c>
+      <c r="D114">
+        <v>86</v>
+      </c>
+      <c r="E114" t="s">
+        <v>26</v>
+      </c>
+      <c r="F114">
+        <v>35585</v>
+      </c>
+      <c r="G114">
+        <v>25</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114">
+        <v>1173</v>
+      </c>
+      <c r="J114">
+        <v>33</v>
+      </c>
+      <c r="K114">
+        <v>14</v>
+      </c>
+      <c r="L114">
+        <v>11</v>
+      </c>
+      <c r="M114">
+        <v>2</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114" s="4">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="P114" s="4">
+        <v>9.1435185185185185E-4</v>
+      </c>
+      <c r="Q114" s="5">
+        <v>2.81E-2</v>
+      </c>
+      <c r="R114" s="5">
+        <v>0.42420000000000002</v>
+      </c>
+      <c r="S114" s="5">
+        <v>0.78569999999999995</v>
+      </c>
+      <c r="T114">
+        <v>1</v>
+      </c>
+      <c r="U114" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="V114" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="W114">
+        <v>3.234</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B115">
+        <v>12</v>
+      </c>
+      <c r="C115">
+        <v>81</v>
+      </c>
+      <c r="D115">
+        <v>85</v>
+      </c>
+      <c r="E115" t="s">
+        <v>27</v>
+      </c>
+      <c r="F115">
+        <v>9736</v>
+      </c>
+      <c r="G115">
+        <v>25</v>
+      </c>
+      <c r="H115">
+        <v>10</v>
+      </c>
+      <c r="I115">
+        <v>45775</v>
+      </c>
+      <c r="J115">
+        <v>534</v>
+      </c>
+      <c r="K115">
+        <v>118</v>
+      </c>
+      <c r="L115">
+        <v>52</v>
+      </c>
+      <c r="M115">
+        <v>63</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115" s="4">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="P115" s="4">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="Q115" s="5">
+        <v>1.17E-2</v>
+      </c>
+      <c r="R115" s="5">
+        <v>0.221</v>
+      </c>
+      <c r="S115" s="5">
+        <v>0.44069999999999998</v>
+      </c>
+      <c r="T115">
+        <v>3</v>
+      </c>
+      <c r="U115" s="5">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="V115" s="5">
+        <v>1</v>
+      </c>
+      <c r="W115">
+        <v>88.8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B116">
+        <v>12</v>
+      </c>
+      <c r="C116">
+        <v>84</v>
+      </c>
+      <c r="D116">
+        <v>86</v>
+      </c>
+      <c r="E116" t="s">
+        <v>26</v>
+      </c>
+      <c r="F116">
+        <v>35585</v>
+      </c>
+      <c r="G116">
+        <v>25</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+      <c r="I116">
+        <v>2183</v>
+      </c>
+      <c r="J116">
+        <v>54</v>
+      </c>
+      <c r="K116">
+        <v>10</v>
+      </c>
+      <c r="L116">
+        <v>5</v>
+      </c>
+      <c r="M116">
+        <v>5</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116" s="4">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="P116" s="4">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="Q116" s="5">
+        <v>2.47E-2</v>
+      </c>
+      <c r="R116" s="5">
+        <v>0.1852</v>
+      </c>
+      <c r="S116" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="T116">
+        <v>0</v>
+      </c>
+      <c r="U116" s="3">
+        <v>0</v>
+      </c>
+      <c r="V116" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="W116">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B117">
+        <v>13</v>
+      </c>
+      <c r="C117">
+        <v>81</v>
+      </c>
+      <c r="D117">
+        <v>85</v>
+      </c>
+      <c r="E117" t="s">
+        <v>27</v>
+      </c>
+      <c r="F117">
+        <v>9736</v>
+      </c>
+      <c r="G117">
+        <v>25</v>
+      </c>
+      <c r="H117">
+        <v>8</v>
+      </c>
+      <c r="I117">
+        <v>42602</v>
+      </c>
+      <c r="J117">
+        <v>445</v>
+      </c>
+      <c r="K117">
+        <v>100</v>
+      </c>
+      <c r="L117">
+        <v>42</v>
+      </c>
+      <c r="M117">
+        <v>55</v>
+      </c>
+      <c r="N117">
+        <v>1</v>
+      </c>
+      <c r="O117" s="4">
+        <v>1.0995370370370371E-3</v>
+      </c>
+      <c r="P117" s="4">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="Q117" s="5">
+        <v>1.04E-2</v>
+      </c>
+      <c r="R117" s="5">
+        <v>0.22470000000000001</v>
+      </c>
+      <c r="S117" s="3">
+        <v>0.42</v>
+      </c>
+      <c r="T117">
+        <v>3</v>
+      </c>
+      <c r="U117" s="5">
+        <v>5.1700000000000003E-2</v>
+      </c>
+      <c r="V117" s="5">
+        <v>0.89829999999999999</v>
+      </c>
+      <c r="W117">
+        <v>42.81</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B118">
+        <v>13</v>
+      </c>
+      <c r="C118">
+        <v>84</v>
+      </c>
+      <c r="D118">
+        <v>86</v>
+      </c>
+      <c r="E118" t="s">
+        <v>26</v>
+      </c>
+      <c r="F118">
+        <v>35585</v>
+      </c>
+      <c r="G118">
+        <v>25</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118">
+        <v>3237</v>
+      </c>
+      <c r="J118">
+        <v>49</v>
+      </c>
+      <c r="K118">
+        <v>12</v>
+      </c>
+      <c r="L118">
+        <v>5</v>
+      </c>
+      <c r="M118">
+        <v>7</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118" s="4">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="P118" s="4">
+        <v>8.2175925925925927E-4</v>
+      </c>
+      <c r="Q118" s="5">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="R118" s="5">
+        <v>0.24490000000000001</v>
+      </c>
+      <c r="S118" s="5">
+        <v>0.41670000000000001</v>
+      </c>
+      <c r="T118">
+        <v>0</v>
+      </c>
+      <c r="U118" s="3">
+        <v>0</v>
+      </c>
+      <c r="V118" s="5">
+        <v>0.88890000000000002</v>
+      </c>
+      <c r="W118">
+        <v>4.0259999999999998</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B119">
+        <v>14</v>
+      </c>
+      <c r="C119">
+        <v>81</v>
+      </c>
+      <c r="D119">
+        <v>85</v>
+      </c>
+      <c r="E119" t="s">
+        <v>27</v>
+      </c>
+      <c r="F119">
+        <v>9736</v>
+      </c>
+      <c r="G119">
+        <v>25</v>
+      </c>
+      <c r="H119">
+        <v>9</v>
+      </c>
+      <c r="I119">
+        <v>26039</v>
+      </c>
+      <c r="J119">
+        <v>181</v>
+      </c>
+      <c r="K119">
+        <v>32</v>
+      </c>
+      <c r="L119">
+        <v>17</v>
+      </c>
+      <c r="M119">
+        <v>15</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119" s="4">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="P119" s="4">
+        <v>8.9120370370370373E-4</v>
+      </c>
+      <c r="Q119" s="5">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="R119" s="5">
+        <v>0.17680000000000001</v>
+      </c>
+      <c r="S119" s="5">
+        <v>0.53129999999999999</v>
+      </c>
+      <c r="T119">
+        <v>0</v>
+      </c>
+      <c r="U119" s="3">
+        <v>0</v>
+      </c>
+      <c r="V119" s="5">
+        <v>1</v>
+      </c>
+      <c r="W119">
+        <v>21.515999999999998</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B120">
+        <v>14</v>
+      </c>
+      <c r="C120">
+        <v>84</v>
+      </c>
+      <c r="D120">
+        <v>86</v>
+      </c>
+      <c r="E120" t="s">
+        <v>26</v>
+      </c>
+      <c r="F120">
+        <v>35585</v>
+      </c>
+      <c r="G120">
+        <v>25</v>
+      </c>
+      <c r="H120">
+        <v>4</v>
+      </c>
+      <c r="I120">
+        <v>3765</v>
+      </c>
+      <c r="J120">
+        <v>67</v>
+      </c>
+      <c r="K120">
+        <v>12</v>
+      </c>
+      <c r="L120">
+        <v>5</v>
+      </c>
+      <c r="M120">
+        <v>7</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120" s="4">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="P120" s="4">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="Q120" s="5">
+        <v>1.78E-2</v>
+      </c>
+      <c r="R120" s="5">
+        <v>0.17910000000000001</v>
+      </c>
+      <c r="S120" s="5">
+        <v>0.41670000000000001</v>
+      </c>
+      <c r="T120">
+        <v>0</v>
+      </c>
+      <c r="U120" s="3">
+        <v>0</v>
+      </c>
+      <c r="V120" s="5">
+        <v>1</v>
+      </c>
+      <c r="W120">
+        <v>5.5739999999999998</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B121">
+        <v>15</v>
+      </c>
+      <c r="C121">
+        <v>81</v>
+      </c>
+      <c r="D121">
+        <v>85</v>
+      </c>
+      <c r="E121" t="s">
+        <v>27</v>
+      </c>
+      <c r="F121">
+        <v>9736</v>
+      </c>
+      <c r="G121">
+        <v>25</v>
+      </c>
+      <c r="H121">
+        <v>10</v>
+      </c>
+      <c r="I121">
+        <v>49318</v>
+      </c>
+      <c r="J121">
+        <v>599</v>
+      </c>
+      <c r="K121">
+        <v>128</v>
+      </c>
+      <c r="L121">
+        <v>55</v>
+      </c>
+      <c r="M121">
+        <v>71</v>
+      </c>
+      <c r="N121">
+        <v>4</v>
+      </c>
+      <c r="O121" s="4">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="P121" s="4">
+        <v>1.0185185185185184E-3</v>
+      </c>
+      <c r="Q121" s="5">
+        <v>1.21E-2</v>
+      </c>
+      <c r="R121" s="5">
+        <v>0.2137</v>
+      </c>
+      <c r="S121" s="5">
+        <v>0.42970000000000003</v>
+      </c>
+      <c r="T121">
+        <v>2</v>
+      </c>
+      <c r="U121" s="5">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="V121" s="5">
+        <v>1</v>
+      </c>
+      <c r="W121">
+        <v>86.34</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B122">
+        <v>15</v>
+      </c>
+      <c r="C122">
+        <v>84</v>
+      </c>
+      <c r="D122">
+        <v>86</v>
+      </c>
+      <c r="E122" t="s">
+        <v>26</v>
+      </c>
+      <c r="F122">
+        <v>35585</v>
+      </c>
+      <c r="G122">
+        <v>25</v>
+      </c>
+      <c r="H122">
+        <v>4</v>
+      </c>
+      <c r="I122">
+        <v>3187</v>
+      </c>
+      <c r="J122">
+        <v>71</v>
+      </c>
+      <c r="K122">
+        <v>23</v>
+      </c>
+      <c r="L122">
+        <v>8</v>
+      </c>
+      <c r="M122">
+        <v>15</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122" s="4">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="P122" s="4">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="Q122" s="5">
+        <v>2.23E-2</v>
+      </c>
+      <c r="R122" s="5">
+        <v>0.32390000000000002</v>
+      </c>
+      <c r="S122" s="5">
+        <v>0.3478</v>
+      </c>
+      <c r="T122">
+        <v>0</v>
+      </c>
+      <c r="U122" s="3">
+        <v>0</v>
+      </c>
+      <c r="V122" s="5">
+        <v>1</v>
+      </c>
+      <c r="W122">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B123">
+        <v>16</v>
+      </c>
+      <c r="C123">
+        <v>81</v>
+      </c>
+      <c r="D123">
+        <v>85</v>
+      </c>
+      <c r="E123" t="s">
+        <v>27</v>
+      </c>
+      <c r="F123">
+        <v>9736</v>
+      </c>
+      <c r="G123">
+        <v>25</v>
+      </c>
+      <c r="H123">
+        <v>7</v>
+      </c>
+      <c r="I123">
+        <v>36538</v>
+      </c>
+      <c r="J123">
+        <v>412</v>
+      </c>
+      <c r="K123">
+        <v>116</v>
+      </c>
+      <c r="L123">
+        <v>63</v>
+      </c>
+      <c r="M123">
+        <v>52</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123" s="4">
+        <v>1.0069444444444444E-3</v>
+      </c>
+      <c r="P123" s="4">
+        <v>1.0416666666666667E-3</v>
+      </c>
+      <c r="Q123" s="5">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="R123" s="5">
+        <v>0.28160000000000002</v>
+      </c>
+      <c r="S123" s="5">
+        <v>0.54310000000000003</v>
+      </c>
+      <c r="T123">
+        <v>1</v>
+      </c>
+      <c r="U123" s="5">
+        <v>1.89E-2</v>
+      </c>
+      <c r="V123" s="5">
+        <v>1</v>
+      </c>
+      <c r="W123">
+        <v>50.195999999999998</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B124">
+        <v>16</v>
+      </c>
+      <c r="C124">
+        <v>84</v>
+      </c>
+      <c r="D124">
+        <v>86</v>
+      </c>
+      <c r="E124" t="s">
+        <v>26</v>
+      </c>
+      <c r="F124">
+        <v>35585</v>
+      </c>
+      <c r="G124">
+        <v>25</v>
+      </c>
+      <c r="H124">
+        <v>3</v>
+      </c>
+      <c r="I124">
+        <v>2942</v>
+      </c>
+      <c r="J124">
+        <v>88</v>
+      </c>
+      <c r="K124">
+        <v>17</v>
+      </c>
+      <c r="L124">
+        <v>3</v>
+      </c>
+      <c r="M124">
+        <v>14</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124" s="4">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="P124" s="4">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="Q124" s="5">
+        <v>2.9899999999999999E-2</v>
+      </c>
+      <c r="R124" s="5">
+        <v>0.19320000000000001</v>
+      </c>
+      <c r="S124" s="5">
+        <v>0.17649999999999999</v>
+      </c>
+      <c r="T124">
+        <v>0</v>
+      </c>
+      <c r="U124" s="3">
+        <v>0</v>
+      </c>
+      <c r="V124" s="5">
+        <v>1</v>
+      </c>
+      <c r="W124">
+        <v>7.008</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B125">
+        <v>17</v>
+      </c>
+      <c r="C125">
+        <v>81</v>
+      </c>
+      <c r="D125">
+        <v>85</v>
+      </c>
+      <c r="E125" t="s">
+        <v>27</v>
+      </c>
+      <c r="F125">
+        <v>9736</v>
+      </c>
+      <c r="G125">
+        <v>25</v>
+      </c>
+      <c r="H125">
+        <v>4</v>
+      </c>
+      <c r="I125">
+        <v>25875</v>
+      </c>
+      <c r="J125">
+        <v>186</v>
+      </c>
+      <c r="K125">
+        <v>57</v>
+      </c>
+      <c r="L125">
+        <v>30</v>
+      </c>
+      <c r="M125">
+        <v>24</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125" s="4">
+        <v>1.5972222222222223E-3</v>
+      </c>
+      <c r="P125" s="4">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="Q125" s="5">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="R125" s="5">
+        <v>0.30649999999999999</v>
+      </c>
+      <c r="S125" s="5">
+        <v>0.52629999999999999</v>
+      </c>
+      <c r="T125">
+        <v>3</v>
+      </c>
+      <c r="U125" s="5">
+        <v>0.1111</v>
+      </c>
+      <c r="V125" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="W125">
+        <v>19.074000000000002</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B126">
+        <v>17</v>
+      </c>
+      <c r="C126">
+        <v>84</v>
+      </c>
+      <c r="D126">
+        <v>86</v>
+      </c>
+      <c r="E126" t="s">
+        <v>26</v>
+      </c>
+      <c r="F126">
+        <v>35585</v>
+      </c>
+      <c r="G126">
+        <v>11</v>
+      </c>
+      <c r="H126">
+        <v>2</v>
+      </c>
+      <c r="I126">
+        <v>485</v>
+      </c>
+      <c r="J126">
+        <v>11</v>
+      </c>
+      <c r="K126">
+        <v>3</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>3</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126" s="4">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="P126" s="4">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="Q126" s="5">
+        <v>2.2700000000000001E-2</v>
+      </c>
+      <c r="R126" s="5">
+        <v>0.2727</v>
+      </c>
+      <c r="S126" s="3">
+        <v>0</v>
+      </c>
+      <c r="T126">
+        <v>0</v>
+      </c>
+      <c r="U126" s="3">
+        <v>0</v>
+      </c>
+      <c r="V126" s="5">
+        <v>1</v>
+      </c>
+      <c r="W126">
+        <v>1.452</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B127">
+        <v>18</v>
+      </c>
+      <c r="C127">
+        <v>81</v>
+      </c>
+      <c r="D127">
+        <v>85</v>
+      </c>
+      <c r="E127" t="s">
+        <v>27</v>
+      </c>
+      <c r="F127">
+        <v>9736</v>
+      </c>
+      <c r="G127">
+        <v>1</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>196</v>
+      </c>
+      <c r="J127">
+        <v>1</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127" s="4">
+        <v>2.2569444444444442E-3</v>
+      </c>
+      <c r="P127" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q127" s="5">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="R127" s="3">
+        <v>1</v>
+      </c>
+      <c r="S127" s="3">
+        <v>1</v>
+      </c>
+      <c r="T127">
+        <v>0</v>
+      </c>
+      <c r="U127" t="s">
+        <v>25</v>
+      </c>
+      <c r="V127" t="s">
+        <v>25</v>
+      </c>
+      <c r="W127">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B128">
+        <v>18</v>
+      </c>
+      <c r="C128">
+        <v>84</v>
+      </c>
+      <c r="D128">
+        <v>86</v>
+      </c>
+      <c r="E128" t="s">
+        <v>26</v>
+      </c>
+      <c r="F128">
+        <v>35585</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>5</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128" t="s">
+        <v>24</v>
+      </c>
+      <c r="P128" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q128" s="3">
+        <v>0</v>
+      </c>
+      <c r="R128" t="s">
+        <v>25</v>
+      </c>
+      <c r="S128" t="s">
+        <v>25</v>
+      </c>
+      <c r="T128">
+        <v>0</v>
+      </c>
+      <c r="U128" t="s">
+        <v>25</v>
+      </c>
+      <c r="V128" t="s">
         <v>25</v>
       </c>
     </row>
@@ -7980,7 +9255,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" customWidth="1"/>
     <col min="4" max="4" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.33203125" bestFit="1" customWidth="1"/>
